--- a/docs/misc/project-work/StatPhi - Priorizacion de Requisitos.xlsx
+++ b/docs/misc/project-work/StatPhi - Priorizacion de Requisitos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonel\Desktop\Proyectos Programacion\JavaScript\statphi-backend\docs\misc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonel\Desktop\Proyectos Programacion\JavaScript\statphi-backend\docs\misc\project-work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058BB57D-A07F-4A81-9DCA-F9BBDC834698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B1D1E4-90BB-4750-8BAF-F5057D001DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D14E2941-2113-460C-8B13-E1BF74064C3B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D14E2941-2113-460C-8B13-E1BF74064C3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Priorizacion" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="268">
   <si>
     <t>R01.1</t>
   </si>
@@ -968,7 +968,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1001,11 +1001,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1343,7 +1338,7 @@
   <dimension ref="A1:G245"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.28515625" customWidth="1"/>
     <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" customWidth="1"/>
@@ -1444,7 +1439,7 @@
       </c>
       <c r="G5" s="1">
         <f>COUNTIF(C2:C245,"Could Have")</f>
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1465,7 +1460,7 @@
       </c>
       <c r="G6" s="1">
         <f>COUNTIF(C2:C245,"Won't Have")</f>
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1484,9 +1479,9 @@
       <c r="F7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="1">
         <f>COUNTIF(C2:C245,"-")</f>
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1505,7 +1500,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1">
         <f>SUM(G3:G7)</f>
-        <v>221</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1567,7 +1562,7 @@
       </c>
       <c r="F12" s="2">
         <f>COUNTIF(B2:B245,E12)</f>
-        <v>180</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1585,7 +1580,7 @@
       </c>
       <c r="F13" s="2">
         <f>COUNTIF(B2:B245,E13)</f>
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1603,7 +1598,7 @@
       </c>
       <c r="F14" s="2">
         <f>SUM(F12:F13)</f>
-        <v>221</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3740,7 +3735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>181</v>
       </c>
@@ -3751,7 +3746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>182</v>
       </c>
@@ -3762,7 +3757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
         <v>227</v>
       </c>
@@ -3773,7 +3768,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>228</v>
       </c>
@@ -3784,7 +3779,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>229</v>
       </c>
@@ -3795,7 +3790,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>231</v>
       </c>
@@ -3806,7 +3801,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
         <v>232</v>
       </c>
@@ -3817,7 +3812,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>233</v>
       </c>
@@ -3828,7 +3823,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
         <v>234</v>
       </c>
@@ -3839,7 +3834,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>235</v>
       </c>
@@ -3850,7 +3845,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
         <v>236</v>
       </c>
@@ -3861,19 +3856,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>243</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D220" s="12"/>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
         <v>244</v>
       </c>
@@ -3883,89 +3877,118 @@
       <c r="C221" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D221" s="12"/>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B222" s="2"/>
-      <c r="C222" s="2"/>
-      <c r="D222" s="12"/>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B222" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B223" s="2"/>
-      <c r="C223" s="13"/>
-      <c r="D223" s="12"/>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B223" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B224" s="2"/>
-      <c r="C224" s="2"/>
-      <c r="D224" s="12"/>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B224" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B225" s="2"/>
-      <c r="C225" s="2"/>
-      <c r="D225" s="12"/>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B225" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B226" s="2"/>
-      <c r="C226" s="2"/>
-      <c r="D226" s="12"/>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B226" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B227" s="2"/>
-      <c r="C227" s="2"/>
-      <c r="D227" s="12"/>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B227" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B228" s="2"/>
-      <c r="C228" s="2"/>
-      <c r="D228" s="12"/>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B228" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="B229" s="2"/>
-      <c r="C229" s="2"/>
-      <c r="D229" s="12"/>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B229" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B230" s="2"/>
-      <c r="C230" s="2"/>
-      <c r="D230" s="12"/>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B230" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="B231" s="2"/>
-      <c r="C231" s="2"/>
-      <c r="D231" s="12"/>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B231" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>241</v>
       </c>
@@ -3975,99 +3998,149 @@
       <c r="C232" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D232" s="12"/>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B233" s="2"/>
-      <c r="C233" s="2"/>
-      <c r="D233" s="12"/>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B233" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="B234" s="1"/>
-      <c r="C234" s="1"/>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B234" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B235" s="1"/>
-      <c r="C235" s="1"/>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B235" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="B236" s="1"/>
-      <c r="C236" s="1"/>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B236" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B237" s="1"/>
-      <c r="C237" s="1"/>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B237" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="B238" s="1"/>
-      <c r="C238" s="1"/>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B238" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B239" s="1"/>
-      <c r="C239" s="1"/>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B239" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="B240" s="1"/>
-      <c r="C240" s="1"/>
+      <c r="B240" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B241" s="1"/>
-      <c r="C241" s="1"/>
+      <c r="B241" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="B242" s="1"/>
-      <c r="C242" s="1"/>
+      <c r="B242" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B243" s="1"/>
-      <c r="C243" s="1"/>
+      <c r="B243" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="B244" s="1"/>
-      <c r="C244" s="1"/>
+      <c r="B244" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="B245" s="1"/>
-      <c r="C245" s="1"/>
+      <c r="B245" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C219" xr:uid="{65280884-1662-49ED-ABCB-FA065C5A7D52}"/>
